--- a/excel/reports.xlsx
+++ b/excel/reports.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\408\Downloads\DigitalSupport-Team-EzKolobok\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\408\Downloads\ks54-techment\DigitalSupport-Team-EzKolobok\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0B8F5FE-DA3E-4310-AD4A-AAAC6F5B4BB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7350357A-241B-4CDD-948A-883C0B12F7B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11685" yWindow="8040" windowWidth="16605" windowHeight="8580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11685" yWindow="6900" windowWidth="16605" windowHeight="8580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="25">
   <si>
     <t>ID</t>
   </si>
@@ -88,6 +88,21 @@
   </si>
   <si>
     <t>Как защитить данные бабушки</t>
+  </si>
+  <si>
+    <t>Бабушка</t>
+  </si>
+  <si>
+    <t>Дедушка</t>
+  </si>
+  <si>
+    <t>Студент</t>
+  </si>
+  <si>
+    <t>Cneltyn</t>
+  </si>
+  <si>
+    <t>Мужчина</t>
   </si>
 </sst>
 </file>
@@ -431,7 +446,7 @@
   <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="33.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="27.28515625" customWidth="1"/>
   </cols>
@@ -457,6 +472,9 @@
       <c r="A2">
         <v>0</v>
       </c>
+      <c r="B2" t="s">
+        <v>20</v>
+      </c>
       <c r="C2" s="1" t="s">
         <v>5</v>
       </c>
@@ -471,6 +489,9 @@
       <c r="A3">
         <v>1</v>
       </c>
+      <c r="B3" t="s">
+        <v>21</v>
+      </c>
       <c r="C3" t="s">
         <v>6</v>
       </c>
@@ -485,6 +506,9 @@
       <c r="A4">
         <v>2</v>
       </c>
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
       <c r="C4" s="1" t="s">
         <v>7</v>
       </c>
@@ -499,6 +523,9 @@
       <c r="A5">
         <v>3</v>
       </c>
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
       <c r="C5" s="1" t="s">
         <v>8</v>
       </c>
@@ -513,6 +540,9 @@
       <c r="A6">
         <v>4</v>
       </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
       <c r="C6" s="1" t="s">
         <v>9</v>
       </c>
@@ -527,6 +557,9 @@
       <c r="A7">
         <v>5</v>
       </c>
+      <c r="B7" t="s">
+        <v>20</v>
+      </c>
       <c r="C7" s="1" t="s">
         <v>10</v>
       </c>
@@ -541,6 +574,9 @@
       <c r="A8">
         <v>6</v>
       </c>
+      <c r="B8" t="s">
+        <v>20</v>
+      </c>
       <c r="C8" s="1" t="s">
         <v>11</v>
       </c>
@@ -555,6 +591,9 @@
       <c r="A9">
         <v>7</v>
       </c>
+      <c r="B9" t="s">
+        <v>20</v>
+      </c>
       <c r="C9" s="1" t="s">
         <v>13</v>
       </c>
@@ -569,6 +608,9 @@
       <c r="A10">
         <v>8</v>
       </c>
+      <c r="B10" t="s">
+        <v>20</v>
+      </c>
       <c r="C10" s="1" t="s">
         <v>12</v>
       </c>
@@ -582,6 +624,9 @@
     <row r="11" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>20</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>19</v>

--- a/excel/reports.xlsx
+++ b/excel/reports.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\408\Downloads\ks54-techment\DigitalSupport-Team-EzKolobok\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7350357A-241B-4CDD-948A-883C0B12F7B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02B66A42-D119-4A60-AF68-5619453A4A40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11685" yWindow="6900" windowWidth="16605" windowHeight="8580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="26">
   <si>
     <t>ID</t>
   </si>
@@ -103,6 +103,9 @@
   </si>
   <si>
     <t>Мужчина</t>
+  </si>
+  <si>
+    <t>AlessandroCool6228</t>
   </si>
 </sst>
 </file>
@@ -626,7 +629,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>19</v>
